--- a/Menu_Cole_setembre_2026.xlsx
+++ b/Menu_Cole_setembre_2026.xlsx
@@ -60,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -70,9 +70,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -439,14 +436,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="78" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -457,20 +453,15 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>primero</t>
+          <t>plato</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>segundo</t>
+          <t>alimentos</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>postre</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nota</t>
         </is>
@@ -484,16 +475,15 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Espaguetis integrals amb salsa de tomàquet / al pesto</t>
+          <t>Espaguetis y croquetas</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Croquetes de pollastre / de bacallà amb remolatxa i pastanaga ratllada</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="3" t="inlineStr"/>
+          <t>Espaguetis:cereales, Tomate:verduras, Croquetas de pollo:proteina_blanca, Remolacha:verduras, Zanahoria:verduras</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -503,16 +493,15 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Arròs del Delta de l'hort (ceba, pebrot i pèsols)</t>
+          <t>Arroz y merluza</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Ventresca de lluç al forn amb rodanxes de carbassó a la planxa</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="3" t="inlineStr"/>
+          <t>Arroz:cereales, Cebolla:verduras, Pimiento:verduras, Guisantes:legumbres, Merluza:pescado, Calabacín:verduras</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -522,16 +511,15 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Empedrat de mongeta blanca (tomàquet, cogombre i olives)</t>
+          <t>Alubias y tortilla de queso</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Truita de formatge i patata amb enciam llarg i raves</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="3" t="inlineStr"/>
+          <t>Alubias blancas:legumbres, Tomate:verduras, Pepino:verduras, Aceitunas:permitido, Tortilla de queso:huevos, Lechuga:verduras, Rábano:verduras</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -541,10 +529,9 @@
       </c>
       <c r="B5" s="3" t="inlineStr"/>
       <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Diada — festiu, no hi ha escola</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Diada — festivo, no hay cole</t>
         </is>
       </c>
     </row>
@@ -556,16 +543,15 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Crema de verdures de temporada</t>
+          <t>Crema de verduras y lentejas</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Llenties estofades amb verdures (ceba i pastanaga)</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr"/>
+          <t>Crema de verduras:verduras, Lentejas:legumbres, Cebolla:verduras, Zanahoria:verduras</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -575,16 +561,15 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Tallarines amb salsa casolana de formatges / sofregit de verdures</t>
+          <t>Tallarines y hamburguesa</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Hamburguesa de vedella amb daus de tomàquet amanits</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
+          <t>Tallarines:cereales, Queso:lacteos, Hamburguesa de ternera:carnes_rojas, Tomate:verduras</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -594,16 +579,15 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Amanida de cigrons (tomàquet, cogombre i olives)</t>
+          <t>Ensalada de garbanzos y tortilla</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Truita de patata i ceba amb enciam meravella i blat de moro</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>Garbanzos:legumbres, Tomate:verduras, Pepino:verduras, Aceitunas:permitido, Tortilla de patata:huevos, Lechuga:verduras, Maíz:cereales</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -613,16 +597,15 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Arròs integral al forn amb ceba, pebrot i xampinyons</t>
+          <t>Arroz integral y pescadilla</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Filet de llúcera al forn amb salsa de tomàquet casolana</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+          <t>Arroz integral:cereales, Cebolla:verduras, Pimiento:verduras, Champiñones:verduras, Pescadilla:pescado, Tomate:verduras</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -632,16 +615,15 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Amanida de patata (tomàquet, pastanaga i ou dur)</t>
+          <t>Ensalada de patata y pollo</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Pollastre arrebossat casolà amb amanida d'espinacs baby i panses</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="3" t="inlineStr"/>
+          <t>Patata:cereales, Tomate:verduras, Zanahoria:verduras, Huevo duro:huevos, Pollo empanado:proteina_blanca, Espinacas:verduras, Pasas:fruta</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -651,16 +633,15 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Amanida d'espirals de colors (cogombre, olives i blat de moro)</t>
+          <t>Ensalada de espirales y revuelto de calabacín</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Remenat de carbassó i patata amb col llombarda i pastanaga amanits</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="3" t="inlineStr"/>
+          <t>Espirales:cereales, Pepino:verduras, Aceitunas:permitido, Maíz:cereales, Calabacín:verduras, Patata:cereales, Lombarda:verduras, Zanahoria:verduras</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -670,16 +651,15 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Arròs del Delta amb salsa casolana de tomàquet</t>
+          <t>Arroz y jamoncitos de pollo</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Pernilets de pollastre a les fines herbes amb enciam de tres colors</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="3" t="inlineStr"/>
+          <t>Arroz:cereales, Tomate:verduras, Jamoncitos de pollo:proteina_blanca, Lechuga:verduras</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -689,16 +669,15 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Pèsols amb patata bullida i oli d'oliva</t>
+          <t>Guisantes con patata y pescado al horno</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Peix fogoner al forn amb canonges, raves i pipes</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
+          <t>Guisantes:legumbres, Patata:cereales, Pescado fogonero:pescado, Canónigos:verduras, Rábano:verduras, Pipas:frutos_secos</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -708,10 +687,9 @@
       </c>
       <c r="B14" s="3" t="inlineStr"/>
       <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>La Mercè — festiu, no hi ha escola</t>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>La Mercè — festivo, no hay cole</t>
         </is>
       </c>
     </row>
@@ -723,16 +701,15 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Crema de pastanaga</t>
+          <t>Crema de zanahoria y garbanzos</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Cigrons estofats amb verdures (ceba i pebrot)</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
+          <t>Crema de zanahoria:verduras, Garbanzos:legumbres, Cebolla:verduras, Pimiento:verduras</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -742,16 +719,15 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Espirals amb pesto casolà d'alfàbrega / salsa casolana de tomàquet</t>
+          <t>Espirales al pesto y revuelto de champiñones</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Remenat de xampinyons i patata amb enciam, olives i vinagreta</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
+          <t>Espirales:cereales, Pesto:permitido, Albahaca:verduras, Champiñones:verduras, Patata:cereales, Lechuga:verduras, Aceitunas:permitido</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -761,16 +737,15 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Vichyssoise</t>
+          <t>Vichyssoise y lentejas</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Llenties saltades amb albergínia i ceba</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="3" t="inlineStr"/>
+          <t>Vichyssoise:verduras, Puerro:verduras, Patata:cereales, Lentejas:legumbres, Berenjena:verduras, Cebolla:verduras</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -780,16 +755,15 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Arròs integral tres delícies (pastanaga, blat de moro i pèsols)</t>
+          <t>Arroz tres delicias y pavo</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Daus de gall dindi marinats amb tomàquet amanit i orenga</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="3" t="inlineStr"/>
+          <t>Arroz integral:cereales, Zanahoria:verduras, Maíz:cereales, Guisantes:legumbres, Pavo:proteina_blanca, Tomate:verduras</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
